--- a/Relatorio_CNDs_Global.xlsx
+++ b/Relatorio_CNDs_Global.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -35,8 +35,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF08A"/>
-        <bgColor rgb="00FEF08A"/>
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
     <fill>
@@ -45,8 +45,14 @@
         <bgColor rgb="0086EFAC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F87171"/>
+        <bgColor rgb="00F87171"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,14 +60,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,6 +450,13 @@
   </sheetPr>
   <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -477,7 +505,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>13.03.27</t>
+          <t>13/03/27</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -496,7 +524,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>21.01.27</t>
+          <t>21/01/27</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -515,7 +543,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -526,23 +554,27 @@
       <c r="E5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>FGTS</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>29.09.26</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Negativa</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>29/09/26</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Vence em 1 dias</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Fique atento, a certidão vencerá em breve.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr"/>
@@ -553,7 +585,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23.10.26</t>
+          <t>23/10/26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -572,7 +604,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21.01.27</t>
+          <t>21/01/27</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -591,7 +623,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22.12.26</t>
+          <t>22/12/26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -602,19 +634,19 @@
       <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr"/>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Águas Lindas</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr"/>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Falha na Coleta</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Bloqueio: Não foi possível emitir a Certidão, por favor procure o setor de arrecadação</t>
         </is>
@@ -640,7 +672,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -659,7 +691,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21.01.27</t>
+          <t>21/01/27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -678,7 +710,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -697,7 +729,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13.10.26</t>
+          <t>13/10/26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -716,7 +748,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>23.10.26</t>
+          <t>23/10/26</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -735,7 +767,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21.01.27</t>
+          <t>21/01/27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -746,19 +778,19 @@
       <c r="E17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr"/>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Águas Lindas</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr"/>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Falha na Coleta</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Bloqueio: Não foi possível emitir a Certidão, por favor procure o setor de arrecadação</t>
         </is>
@@ -784,7 +816,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -803,7 +835,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21.01.27</t>
+          <t>21/01/27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -822,7 +854,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -841,7 +873,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13.10.26</t>
+          <t>13/10/26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -860,7 +892,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23.10.26</t>
+          <t>23/10/26</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -879,7 +911,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>21.01.27</t>
+          <t>21/01/27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -898,7 +930,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>22.12.26</t>
+          <t>22/12/26</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -917,7 +949,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22.12.26</t>
+          <t>22/12/26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -947,7 +979,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -966,7 +998,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>21.01.27</t>
+          <t>21/01/27</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -985,7 +1017,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -996,23 +1028,27 @@
       <c r="E31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>FGTS</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>04.10.26</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Negativa</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>Vence em 6 dias</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Fique atento, a certidão vencerá em breve.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr"/>
@@ -1023,7 +1059,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>23.10.26</t>
+          <t>23/10/26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1042,7 +1078,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>21.01.27</t>
+          <t>21/01/27</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1061,7 +1097,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>22.12.26</t>
+          <t>22/12/26</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1080,7 +1116,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>23.10.26</t>
+          <t>23/10/26</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1110,7 +1146,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1129,7 +1165,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>22.01.27</t>
+          <t>22/01/27</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1148,7 +1184,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>23.03.27</t>
+          <t>23/03/27</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1167,7 +1203,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>11.10.26</t>
+          <t>11/10/26</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1186,7 +1222,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>24.10.26</t>
+          <t>24/10/26</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1205,7 +1241,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>22.01.27</t>
+          <t>22/01/27</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1250,7 +1286,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1269,7 +1305,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>22.01.27</t>
+          <t>22/01/27</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1288,7 +1324,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>23.03.27</t>
+          <t>23/03/27</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1307,7 +1343,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>11.10.26</t>
+          <t>11/10/26</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1326,7 +1362,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>24.10.26</t>
+          <t>24/10/26</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1345,7 +1381,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>22.01.27</t>
+          <t>22/01/27</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1356,19 +1392,19 @@
       <c r="E51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr"/>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Formosa</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr"/>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Falha na Coleta</t>
         </is>
       </c>
-      <c r="E52" s="1" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Bloqueio: Contribuinte possui valores em aberto vencidos, favor procurar a prefeitura!</t>
         </is>
@@ -1394,7 +1430,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>22.03.27</t>
+          <t>22/03/27</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1413,7 +1449,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>22.01.27</t>
+          <t>22/01/27</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1432,7 +1468,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>23.03.27</t>
+          <t>23/03/27</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1451,7 +1487,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>13.10.26</t>
+          <t>13/10/26</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1470,7 +1506,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>24.10.26</t>
+          <t>24/10/26</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1489,7 +1525,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>22.01.27</t>
+          <t>22/01/27</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1508,7 +1544,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>23.12.26</t>
+          <t>23/12/26</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -1519,19 +1555,19 @@
       <c r="E60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr"/>
-      <c r="B61" s="1" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr"/>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Formosa</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr"/>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Falha na Coleta</t>
         </is>
       </c>
-      <c r="E61" s="1" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Bloqueio: Contribuinte possui valores em aberto vencidos, favor procurar a prefeitura!</t>
         </is>
@@ -1549,109 +1585,137 @@
       <c r="E62" s="1" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr"/>
-      <c r="B63" s="1" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr"/>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E63" s="1" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>22/03/27</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr"/>
-      <c r="B64" s="1" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr"/>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>23/01/27</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr"/>
-      <c r="B65" s="1" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Trabalhista</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr"/>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>24/03/27</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr"/>
-      <c r="B66" s="1" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>FGTS</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr"/>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>13/10/26</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr"/>
-      <c r="B67" s="1" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Comprasnet</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr"/>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>25/10/26</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr"/>
-      <c r="B68" s="1" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>AGEHAB</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr"/>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>23/01/27</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr"/>
-      <c r="B69" s="1" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Águas Lindas</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr"/>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>25/10/26</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1665,109 +1729,137 @@
       <c r="E70" s="1" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr"/>
-      <c r="B71" s="1" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr"/>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>22/03/27</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr"/>
-      <c r="B72" s="1" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr"/>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>23/01/27</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr"/>
-      <c r="B73" s="1" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Trabalhista</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr"/>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>24/03/27</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr"/>
-      <c r="B74" s="1" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>FGTS</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr"/>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>13/10/26</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr"/>
-      <c r="B75" s="1" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Comprasnet</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr"/>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>25/10/26</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr"/>
-      <c r="B76" s="1" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>AGEHAB</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr"/>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>23/01/27</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr"/>
-      <c r="B77" s="1" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Águas Lindas</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr"/>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>25/10/26</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Positiva com Efeito Negativo</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1781,124 +1873,156 @@
       <c r="E78" s="1" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr"/>
-      <c r="B79" s="1" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr"/>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>22/03/27</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="1" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr"/>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>23/01/27</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr"/>
-      <c r="B81" s="1" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Trabalhista</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr"/>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>24/03/27</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>FGTS</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>13/10/26</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="1" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Comprasnet</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>25/10/26</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr"/>
-      <c r="B84" s="1" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>AGEHAB</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>23/01/27</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="1" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Estadual DF</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>24/12/26</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="1" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr"/>
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>Formosa</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Falha na Coleta</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>CNPJ não cadastrado ou sem débitos encontrados.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -1912,109 +2036,137 @@
       <c r="E87" s="1" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr"/>
-      <c r="B88" s="1" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>22/03/27</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Positiva com Efeito Negativo</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr"/>
-      <c r="B89" s="1" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>23/01/27</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr"/>
-      <c r="B90" s="1" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Trabalhista</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr"/>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>24/03/27</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr"/>
-      <c r="B91" s="1" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>FGTS</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>13/10/26</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr"/>
-      <c r="B92" s="1" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Comprasnet</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr"/>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>25/10/26</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="inlineStr"/>
-      <c r="B93" s="1" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>AGEHAB</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr"/>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>23/01/27</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr"/>
-      <c r="B94" s="1" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Formosa</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr"/>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>24/12/26</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
